--- a/output/pdf_financials_xlsx/KNG.xlsx
+++ b/output/pdf_financials_xlsx/KNG.xlsx
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.981277</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.062421</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.159578</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.159638</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.159638</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.159638</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.159638</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.159638</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.159638</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.159638</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.159638</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.159638</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.159638</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.463838</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.575509</v>
       </c>
     </row>
     <row r="93">
@@ -6916,16 +6916,16 @@
         <v>0</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.113194</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.214079</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.119762</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-1.395764</v>
       </c>
     </row>
     <row r="119">
@@ -8788,7 +8788,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -12065,7 +12069,11 @@
           <t>Share-based payment reserve 2,062,421</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>1.981277</v>
       </c>
@@ -12917,7 +12925,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -13763,7 +13775,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KNG.xlsx
+++ b/output/pdf_financials_xlsx/KNG.xlsx
@@ -972,19 +972,19 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008288999999999999</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.009327</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.009277000000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.010793</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.007178</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -999,19 +999,19 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.005383</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.02139</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.057259</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.038286</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.046654</v>
       </c>
     </row>
     <row r="13">
@@ -1902,19 +1902,19 @@
         <v>-0.547863</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.056764</v>
+        <v>-1.065053</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.71736</v>
+        <v>-2.726687</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.432643</v>
+        <v>-0.44192</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.429586</v>
+        <v>-2.440379</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.229219</v>
+        <v>-0.236397</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.190398</v>
@@ -1929,19 +1929,19 @@
         <v>-0.336336</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.188965</v>
+        <v>-0.194348</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.010722</v>
+        <v>-0.032112</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.47953</v>
+        <v>-0.536789</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.790113</v>
+        <v>-0.828399</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.796837</v>
+        <v>-0.843491</v>
       </c>
     </row>
     <row r="28">
@@ -2006,19 +2006,19 @@
         <v>-0.541219</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.044404</v>
+        <v>-1.052693</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.714159</v>
+        <v>-2.723486</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.432643</v>
+        <v>-0.44192</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.429586</v>
+        <v>-2.440379</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.229219</v>
+        <v>-0.236397</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.190398</v>
@@ -2033,19 +2033,19 @@
         <v>-0.336336</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.188965</v>
+        <v>-0.194348</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.010722</v>
+        <v>-0.032112</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.47953</v>
+        <v>-0.536789</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.790113</v>
+        <v>-0.828399</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.796837</v>
+        <v>-0.843491</v>
       </c>
     </row>
     <row r="30">
@@ -2278,49 +2278,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.265713</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.685483</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.833433</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.882221</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.780952</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.575522</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.382145</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.249061</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.570554</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.705215</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.891799</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.800619</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.908857</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.253296</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>4.311562</v>
       </c>
     </row>
     <row r="35">
@@ -2382,49 +2382,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.265713</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.685483</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.833433</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.882221</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.780952</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.575522</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.382145</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.249061</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.570554</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.705215</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.891799</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.800619</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.908857</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.253296</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>4.311562</v>
       </c>
     </row>
     <row r="37">
@@ -3006,49 +3006,49 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.270375</v>
+        <v>0.004662</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.690062</v>
+        <v>0.004579</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.882391</v>
+        <v>0.048958</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.8843760000000001</v>
+        <v>0.002155</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.782342</v>
+        <v>0.00139</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.576389</v>
+        <v>0.000867</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.384712</v>
+        <v>0.002567</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.251628</v>
+        <v>0.002567</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.583939</v>
+        <v>0.013385</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.7192539999999999</v>
+        <v>0.014039</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.901832</v>
+        <v>0.010033</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.811248</v>
+        <v>0.010629</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.930261</v>
+        <v>0.021404</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.323222</v>
+        <v>0.069926</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>4.351237</v>
+        <v>0.039675</v>
       </c>
     </row>
     <row r="49">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
@@ -17717,7 +17717,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
